--- a/Retired Styles-Batch 1.xlsx
+++ b/Retired Styles-Batch 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F3DA7C-3591-4D95-8140-6B09C386BD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62638768-A524-4C5A-AEEA-A022F48FB98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1230,9 +1230,6 @@
     <t xml:space="preserve">Vivo Yene Wide Leg Pants </t>
   </si>
   <si>
-    <t xml:space="preserve">Vivo Ava Front Pleat Knee Length Dress In Crepe </t>
-  </si>
-  <si>
     <t xml:space="preserve">Vivo Jersey Drop Shoulder Top </t>
   </si>
   <si>
@@ -1242,9 +1239,6 @@
     <t xml:space="preserve">Vivo Essentials Strappy Cold Shoulder Top </t>
   </si>
   <si>
-    <t xml:space="preserve">Vivo Mistari 3/4 Sleeve V - Neck Collared Tunic Top </t>
-  </si>
-  <si>
     <t xml:space="preserve">Vivo Studio 2-piece in Mixed Media </t>
   </si>
   <si>
@@ -1254,10 +1248,16 @@
     <t xml:space="preserve">Vivo J.O V-Neck Sheath Dress </t>
   </si>
   <si>
-    <t>Vivo Basic Liv Chiffon Top - Off</t>
-  </si>
-  <si>
     <t>Style Name</t>
+  </si>
+  <si>
+    <t>Vivo Ava Front Pleat Knee Length Dress</t>
+  </si>
+  <si>
+    <t>Vivo Basic Liv Chiffon Top</t>
+  </si>
+  <si>
+    <t>Vivo Mistari 3/4 Sleeve V</t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1541,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1781,7 +1781,7 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
@@ -1826,7 +1826,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
@@ -1926,12 +1926,12 @@
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
@@ -2006,22 +2006,22 @@
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
